--- a/data/trans_dic/P19C11_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,96</t>
+          <t>4,49; 9,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,28</t>
+          <t>4,3; 8,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 8,57</t>
+          <t>5,07; 8,62</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,66</t>
+          <t>1,53; 4,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,19</t>
+          <t>1,82; 4,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,96</t>
+          <t>1,93; 4,0</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,41</t>
+          <t>2,41; 6,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,56</t>
+          <t>3,07; 6,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,92</t>
+          <t>3,16; 5,71</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,42</t>
+          <t>1,03; 5,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,31</t>
+          <t>0,48; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,83</t>
+          <t>0,88; 2,92</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,25</t>
+          <t>8,04; 16,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 14,33</t>
+          <t>8,62; 14,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 13,73</t>
+          <t>8,83; 13,52</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,67</t>
+          <t>0,38; 2,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,37</t>
+          <t>0,27; 1,41</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,97</t>
+          <t>4,68; 8,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,67</t>
+          <t>2,45; 7,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,47</t>
+          <t>3,32; 7,29</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,06</t>
+          <t>1,06; 4,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,87</t>
+          <t>1,85; 3,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,53</t>
+          <t>1,59; 3,49</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,03</t>
+          <t>3,15; 4,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,49</t>
+          <t>3,14; 4,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,54</t>
+          <t>3,46; 4,53</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13829; 30426</t>
+          <t>13726; 29878</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12974; 26701</t>
+          <t>12375; 25478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30199; 50851</t>
+          <t>30087; 51118</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7212; 23650</t>
+          <t>7739; 23347</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8894; 20996</t>
+          <t>9113; 21414</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19017; 39976</t>
+          <t>19463; 40310</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7271; 19301</t>
+          <t>7263; 19340</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9887; 21981</t>
+          <t>10281; 21393</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20553; 37705</t>
+          <t>20101; 36314</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3807; 16805</t>
+          <t>3203; 15637</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2424; 10937</t>
+          <t>2290; 10525</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7579; 22149</t>
+          <t>6904; 22849</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13683; 27374</t>
+          <t>13537; 27003</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17798; 28988</t>
+          <t>17436; 28738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33683; 50900</t>
+          <t>32735; 50132</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>996; 6782</t>
+          <t>977; 6281</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2057</t>
+          <t>0; 1843</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1226; 6836</t>
+          <t>1350; 7073</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>28438; 53820</t>
+          <t>28043; 52789</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19019; 63551</t>
+          <t>20304; 64732</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51182; 106681</t>
+          <t>47425; 104131</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8340; 36927</t>
+          <t>9638; 37518</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13355; 27271</t>
+          <t>13004; 26924</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25999; 56999</t>
+          <t>25716; 56207</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>111338; 168678</t>
+          <t>105752; 163532</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>113688; 160699</t>
+          <t>112396; 161142</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>236545; 314939</t>
+          <t>239540; 314375</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C11_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,78</t>
+          <t>5,05; 10,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,86</t>
+          <t>4,35; 8,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,62</t>
+          <t>5,15; 8,52</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>2,76%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,61</t>
+          <t>1,56; 4,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,27</t>
+          <t>1,77; 4,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,0</t>
+          <t>1,9; 3,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,42</t>
+          <t>2,39; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,38</t>
+          <t>3,02; 6,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,71</t>
+          <t>3,16; 5,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,04</t>
+          <t>0,95; 4,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,22</t>
+          <t>0,68; 2,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,92</t>
+          <t>1,08; 3,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 16,03</t>
+          <t>7,72; 15,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 14,21</t>
+          <t>8,16; 13,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,52</t>
+          <t>8,77; 13,47</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,48</t>
+          <t>0,38; 2,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,41</t>
+          <t>0,26; 1,42</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,8</t>
+          <t>5,01; 9,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,81</t>
+          <t>5,43; 8,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,29</t>
+          <t>5,68; 8,27</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,13</t>
+          <t>2,31; 4,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,82</t>
+          <t>1,83; 3,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,49</t>
+          <t>2,35; 3,91</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,88</t>
+          <t>3,94; 5,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,5</t>
+          <t>3,71; 4,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,53</t>
+          <t>3,98; 4,86</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39876</t>
+          <t>40958</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13726; 29878</t>
+          <t>15192; 32569</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12375; 25478</t>
+          <t>13455; 25514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30087; 51118</t>
+          <t>31459; 51998</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>29012</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7739; 23347</t>
+          <t>8073; 23744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9113; 21414</t>
+          <t>9419; 21981</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19463; 40310</t>
+          <t>19969; 41132</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>27568</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7263; 19340</t>
+          <t>7170; 19344</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10281; 21393</t>
+          <t>10319; 22493</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20101; 36314</t>
+          <t>20308; 37031</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>14662</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3203; 15637</t>
+          <t>3525; 16606</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290; 10525</t>
+          <t>2872; 11042</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6904; 22849</t>
+          <t>8546; 24293</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>21086</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41853</t>
+          <t>44989</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13537; 27003</t>
+          <t>14615; 30027</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17436; 28738</t>
+          <t>17928; 29868</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32735; 50132</t>
+          <t>35887; 55094</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>372</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3146</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>977; 6281</t>
+          <t>945; 6012</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1843</t>
+          <t>0; 1693</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1350; 7073</t>
+          <t>1300; 7093</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>39631</t>
+          <t>47653</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43479</t>
+          <t>51800</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83110</t>
+          <t>99454</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>28043; 52789</t>
+          <t>34978; 64497</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20304; 64732</t>
+          <t>40264; 65956</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47425; 104131</t>
+          <t>81683; 119013</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>47614</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9638; 37518</t>
+          <t>17785; 37758</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13004; 26924</t>
+          <t>14808; 29681</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25716; 56207</t>
+          <t>37173; 61832</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>152143</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>307405</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>105752; 163532</t>
+          <t>133792; 180390</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>112396; 161142</t>
+          <t>134476; 173205</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>239540; 314375</t>
+          <t>279706; 341573</t>
         </is>
       </c>
     </row>
